--- a/artfynd/A 41279-2024 artfynd.xlsx
+++ b/artfynd/A 41279-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>121095138</v>
       </c>
       <c r="B3" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41279-2024 artfynd.xlsx
+++ b/artfynd/A 41279-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>121095138</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
+        <v>78249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41279-2024 artfynd.xlsx
+++ b/artfynd/A 41279-2024 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>121095138</v>
       </c>
       <c r="B3" t="n">
-        <v>78249</v>
+        <v>78252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41279-2024 artfynd.xlsx
+++ b/artfynd/A 41279-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>91797694</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510404.4131103717</v>
+        <v>510404</v>
       </c>
       <c r="R2" t="n">
-        <v>7002141.874181227</v>
+        <v>7002142</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2020-07-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-07-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,12 +791,7 @@
         <v>121095138</v>
       </c>
       <c r="B3" t="n">
-        <v>78252</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,6 +920,243 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121094927</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Råkmyren, Råkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>510420</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7002092</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På frisk mark. Tidigare brandpåverkad.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121094655</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råkmyren, Råkmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>510467</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7002097</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fire killed tree # Kolad stubbe. # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41279-2024 artfynd.xlsx
+++ b/artfynd/A 41279-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91797694</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121095138</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121094927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1157,8 +1177,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121094655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>